--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104722_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104722_W30.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2763</v>
+        <v>4.9562</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2639</v>
+        <v>4.5779</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0124</v>
+        <v>0.3783</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4175</v>
+        <v>3.4017</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8978</v>
+        <v>-0.9038</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3153</v>
+        <v>4.3055</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7604</v>
+        <v>4.7325</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0562</v>
+        <v>-0.0699</v>
       </c>
       <c r="L2" t="n">
-        <v>4.8166</v>
+        <v>4.8025</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3429</v>
+        <v>-1.3309</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8416</v>
+        <v>-0.8339</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5013</v>
+        <v>-0.497</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0961</v>
+        <v>-0.3984</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9527</v>
+        <v>-0.602</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1434</v>
+        <v>0.2036</v>
       </c>
       <c r="V2" t="n">
-        <v>2.4093</v>
+        <v>2.4082</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5563</v>
+        <v>3.376</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9429</v>
+        <v>3.6844</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3866</v>
+        <v>-0.3084</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7052</v>
+        <v>2.7004</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3885</v>
+        <v>-0.3853</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0937</v>
+        <v>3.0856</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9457</v>
+        <v>3.9314</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0924</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>3.8533</v>
+        <v>3.842</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2405</v>
+        <v>-1.231</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4809</v>
+        <v>-0.4747</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.7563</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0102</v>
+        <v>-0.165</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3216</v>
+        <v>-0.5625</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3318</v>
+        <v>0.3975</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3188</v>
+        <v>0.3155</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>H. ALDERETE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.6192</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0503</v>
+        <v>1.9133</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.21</v>
+        <v>-1.2941</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7534999999999999</v>
+        <v>2.02</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6823</v>
+        <v>0.8297</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0712</v>
+        <v>1.1903</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5923</v>
+        <v>2.2341</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2194</v>
+        <v>0.9308</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3728</v>
+        <v>1.3033</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3457</v>
+        <v>-0.2141</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9016999999999999</v>
+        <v>-0.1011</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.444</v>
+        <v>-0.113</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0447</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0447</v>
+        <v>0.4553</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8671</v>
+        <v>0.3229</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1392</v>
+        <v>-0.3207</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7279</v>
+        <v>0.6437</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.3181</v>
+        <v>-2.1789</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3188</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6369</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. ALDERETE</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5627</v>
+        <v>-0.1836</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6828</v>
+        <v>2.8901</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1201</v>
+        <v>-3.0737</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0183</v>
+        <v>-0.3798</v>
       </c>
       <c r="H5" t="n">
-        <v>0.828</v>
+        <v>1.2201</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1903</v>
+        <v>-1.5999</v>
       </c>
       <c r="J5" t="n">
-        <v>2.238</v>
+        <v>3.017</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9332</v>
+        <v>2.5855</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3048</v>
+        <v>0.4315</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2197</v>
+        <v>-3.3968</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1052</v>
+        <v>-1.3654</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1145</v>
+        <v>-2.0314</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4544</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4544</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2725</v>
+        <v>-0.8525</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5553</v>
+        <v>-0.6717</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8278</v>
+        <v>-0.1808</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.1825</v>
+        <v>-0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1825</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. SHERMADINI</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2681</v>
+        <v>-0.3532</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9993</v>
+        <v>0.2062</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2674</v>
+        <v>-0.5594</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9574</v>
+        <v>-0.7464</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4042</v>
+        <v>-0.6783</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5532</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4662</v>
+        <v>0.5857</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3171</v>
+        <v>0.2133</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1491</v>
+        <v>0.3724</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4237</v>
+        <v>-1.3321</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7023</v>
+        <v>-0.4405</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2272</v>
+        <v>2.0487</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2272</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0078</v>
+        <v>-0.3368</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4419</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5659</v>
+        <v>0.3583</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5456</v>
+        <v>-1.3187</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0913</v>
+        <v>0.3155</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>G. SHERMADINI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7448</v>
+        <v>-0.9627</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6463</v>
+        <v>1.6377</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3911</v>
+        <v>-2.6004</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3828</v>
+        <v>-0.9557</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5319</v>
+        <v>-0.4048</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1491</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3625</v>
+        <v>0.4625</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7342</v>
+        <v>0.3135</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6284</v>
+        <v>0.1489</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9797</v>
+        <v>-1.4182</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2022</v>
+        <v>-0.7184</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7775</v>
+        <v>-0.6998</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6816</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8175</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5585</v>
+        <v>0.3101</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5803</v>
+        <v>0.0858</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0218</v>
+        <v>0.2243</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2507</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2507</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7938</v>
+        <v>-1.1329</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5511</v>
+        <v>1.3891</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3449</v>
+        <v>-2.522</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3833</v>
+        <v>0.3849</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2171</v>
+        <v>0.5339</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6004</v>
+        <v>-0.1489</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0276</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5922</v>
+        <v>1.7269</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4354</v>
+        <v>1.6231</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.4109</v>
+        <v>-2.9651</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.375</v>
+        <v>-1.1931</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.0358</v>
+        <v>-1.772</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5903</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5903</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4552</v>
+        <v>-0.9535</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0221</v>
+        <v>-0.8228</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4331</v>
+        <v>-0.1308</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5456</v>
+        <v>-1.2472</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5456</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0913</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5613</v>
+        <v>-1.4673</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.833</v>
+        <v>-1.8361</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2717</v>
+        <v>0.3688</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5733</v>
+        <v>-1.573</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8017</v>
+        <v>-0.8013</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7716</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.486</v>
+        <v>-1.4876</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7716</v>
+        <v>-0.7724</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7143</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0873</v>
+        <v>-0.0854</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0301</v>
+        <v>-0.0289</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0573</v>
+        <v>-0.0565</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4423</v>
+        <v>-0.3496</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.347</v>
+        <v>-0.3485</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0953</v>
+        <v>-0.0011</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7809</v>
+        <v>-3.9739</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7524</v>
+        <v>-3.1875</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0285</v>
+        <v>-0.7864</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.3747</v>
+        <v>-3.3741</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6778</v>
+        <v>-0.6727</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6969</v>
+        <v>-2.7014</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6561</v>
+        <v>-1.6696</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6973</v>
+        <v>0.6927</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.3534</v>
+        <v>-2.3624</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7186</v>
+        <v>-1.7045</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.375</v>
+        <v>-1.3654</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3435</v>
+        <v>-0.3391</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.861</v>
+        <v>-1.0535</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4386</v>
+        <v>-0.853</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4224</v>
+        <v>-0.2005</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2292</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4782</v>
+        <v>0.4733</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.705</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9701</v>
+        <v>-4.7616</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0278</v>
+        <v>-2.925</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9423</v>
+        <v>-1.8365</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2151</v>
+        <v>-1.2158</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4674</v>
+        <v>-1.4675</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2523</v>
+        <v>0.2517</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0619</v>
+        <v>-0.0701</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1743</v>
+        <v>-1.1796</v>
       </c>
       <c r="L11" t="n">
-        <v>1.1124</v>
+        <v>1.1094</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1532</v>
+        <v>-1.1457</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2931</v>
+        <v>-0.2879</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8601</v>
+        <v>-0.8578</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8175</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.6352</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.5786</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1522</v>
+        <v>-0.0567</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.883500000000002</v>
+        <v>-3.883799999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>8.523399999999999</v>
+        <v>8.350100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.4068</v>
+        <v>-12.2338</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2665000000000002</v>
+        <v>0.2622000000000002</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7427</v>
+        <v>-2.73</v>
       </c>
       <c r="I12" t="n">
-        <v>3.0092</v>
+        <v>2.9922</v>
       </c>
       <c r="J12" t="n">
-        <v>15.1887</v>
+        <v>15.0859</v>
       </c>
       <c r="K12" t="n">
-        <v>4.583700000000001</v>
+        <v>4.530200000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>10.6051</v>
+        <v>10.5555</v>
       </c>
       <c r="M12" t="n">
-        <v>-14.9222</v>
+        <v>-14.8238</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.326099999999999</v>
+        <v>-7.2604</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.5959</v>
+        <v>-7.563400000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>4.5439</v>
+        <v>4.5526</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.8156</v>
+        <v>-6.829000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3595</v>
+        <v>11.3818</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.1018</v>
+        <v>-4.1115</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.3306</v>
+        <v>-5.3691</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2288</v>
+        <v>1.2575</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.591900000000001</v>
+        <v>-4.5869</v>
       </c>
       <c r="W12" t="n">
-        <v>5.480799999999999</v>
+        <v>5.462199999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.0728</v>
+        <v>-10.0493</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.47</v>
+        <v>6.4786</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4964</v>
+        <v>4.7021</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9735</v>
+        <v>1.7765</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6252</v>
+        <v>2.6209</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5553</v>
+        <v>1.5513</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0698</v>
+        <v>1.0696</v>
       </c>
       <c r="J13" t="n">
-        <v>3.534</v>
+        <v>3.5188</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5328</v>
+        <v>1.5233</v>
       </c>
       <c r="L13" t="n">
-        <v>2.0012</v>
+        <v>1.9955</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9089</v>
+        <v>-0.8979</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0225</v>
+        <v>0.028</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9314</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5926</v>
+        <v>1.6168</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3914</v>
+        <v>0.6268</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2012</v>
+        <v>0.99</v>
       </c>
       <c r="V13" t="n">
-        <v>4.7512</v>
+        <v>4.7449</v>
       </c>
       <c r="W13" t="n">
-        <v>3.9788</v>
+        <v>3.9709</v>
       </c>
       <c r="X13" t="n">
-        <v>0.7724</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5591</v>
+        <v>3.9313</v>
       </c>
       <c r="E14" t="n">
-        <v>4.092</v>
+        <v>3.5977</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4671</v>
+        <v>0.3335</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3942</v>
+        <v>3.3928</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6875</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>4.0816</v>
+        <v>4.0818</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1453</v>
+        <v>4.1328</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5522</v>
+        <v>-0.5591</v>
       </c>
       <c r="L14" t="n">
-        <v>4.6974</v>
+        <v>4.6918</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7511</v>
+        <v>-0.74</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1353</v>
+        <v>-0.13</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6158</v>
+        <v>-0.61</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1645</v>
+        <v>1.54</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7639</v>
+        <v>0.2876</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4006</v>
+        <v>1.2525</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3188</v>
+        <v>0.3155</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Y. MORIN</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.639</v>
+        <v>2.3991</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8365</v>
+        <v>4.6082</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8025</v>
+        <v>-2.209</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3077</v>
+        <v>1.9848</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7611</v>
+        <v>3.821</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4534</v>
+        <v>-1.8362</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6937</v>
+        <v>3.6563</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.731</v>
+        <v>4.4536</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0373</v>
+        <v>-0.7973</v>
       </c>
       <c r="M15" t="n">
-        <v>0.386</v>
+        <v>-1.6715</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0301</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4161</v>
+        <v>-1.0389</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2272</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2272</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6282</v>
+        <v>0.1184</v>
       </c>
       <c r="T15" t="n">
-        <v>1.439</v>
+        <v>-0.2954</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1893</v>
+        <v>0.4138</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0913</v>
+        <v>-0.387</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0913</v>
+        <v>1.2472</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>Y. MORIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0307</v>
+        <v>1.691</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0431</v>
+        <v>0.8843</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.0123</v>
+        <v>0.8066</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9912</v>
+        <v>-0.309</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8319</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.8408</v>
+        <v>0.4545</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6757</v>
+        <v>-0.6974</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4706</v>
+        <v>-0.7347</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7949000000000001</v>
+        <v>0.0372</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6846</v>
+        <v>0.3884</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6387</v>
+        <v>-0.0289</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0459</v>
+        <v>0.4173</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6816</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6816</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2558</v>
+        <v>0.6829</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8833</v>
+        <v>0.4923</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3725</v>
+        <v>0.1906</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3862</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2507</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.6369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6235000000000001</v>
+        <v>1.2043</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9325</v>
+        <v>3.2745</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.309</v>
+        <v>-2.0702</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4418</v>
+        <v>1.4442</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8107</v>
+        <v>0.8125</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6311</v>
+        <v>0.6317</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9736</v>
+        <v>3.9647</v>
       </c>
       <c r="K17" t="n">
-        <v>1.78</v>
+        <v>1.7754</v>
       </c>
       <c r="L17" t="n">
-        <v>2.1936</v>
+        <v>2.1893</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5318</v>
+        <v>-2.5205</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9693000000000001</v>
+        <v>-0.9629</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5625</v>
+        <v>-1.5576</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0217</v>
+        <v>-0.4495</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0411</v>
+        <v>-0.6902</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0194</v>
+        <v>0.2407</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.4782</v>
+        <v>-0.4733</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4782</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3144</v>
+        <v>-0.9692</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7546</v>
+        <v>1.1429</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.069</v>
+        <v>-2.1122</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2191</v>
+        <v>-0.2202</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1669</v>
+        <v>2.163</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.386</v>
+        <v>-2.3832</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0515</v>
+        <v>2.0398</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2872</v>
+        <v>2.2785</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2357</v>
+        <v>-0.2388</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2706</v>
+        <v>-2.2599</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1203</v>
+        <v>-0.1155</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.1503</v>
+        <v>-2.1444</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5903</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>1.495</v>
+        <v>0.8444</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8837</v>
+        <v>0.29</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6113</v>
+        <v>0.5543</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6992</v>
+        <v>-1.3944</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9929</v>
+        <v>0.627</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6922</v>
+        <v>-2.0214</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.5711</v>
+        <v>-3.5664</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4261</v>
+        <v>-1.4246</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.145</v>
+        <v>-2.1418</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2844</v>
+        <v>-1.2892</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6446</v>
+        <v>-0.6485</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6398</v>
+        <v>-0.6407</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2867</v>
+        <v>-2.2772</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7814</v>
+        <v>-0.7761</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5052</v>
+        <v>-1.5011</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7806</v>
+        <v>0.0825</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0948</v>
+        <v>-0.2627</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6858</v>
+        <v>0.3452</v>
       </c>
       <c r="V19" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="20">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6795</v>
+        <v>-1.5079</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2016</v>
+        <v>-2.9836</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5221</v>
+        <v>1.4757</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3268</v>
+        <v>-0.3254</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5605</v>
+        <v>1.562</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8874</v>
+        <v>-1.8875</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1364</v>
+        <v>-0.1446</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1924</v>
+        <v>1.1893</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3288</v>
+        <v>-1.334</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1904</v>
+        <v>-0.1808</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3681</v>
+        <v>0.3727</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5585</v>
+        <v>-0.5535</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5903</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.2532</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9527</v>
+        <v>-0.7204</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0309</v>
+        <v>0.9736</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9622</v>
+        <v>-1.6278</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3114</v>
+        <v>-1.2031</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.4246</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7827</v>
+        <v>-0.7834</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3246</v>
+        <v>-1.324</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5419</v>
+        <v>0.5406</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3104</v>
+        <v>0.3045</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2495</v>
+        <v>-1.2518</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5598</v>
+        <v>1.5563</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0931</v>
+        <v>-1.0879</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0752</v>
+        <v>-0.0722</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0179</v>
+        <v>-1.0157</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4979</v>
+        <v>-0.1615</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4858</v>
+        <v>-0.3695</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.012</v>
+        <v>0.208</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8207</v>
+        <v>-2.3518</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9424</v>
+        <v>-0.8313</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8782</v>
+        <v>-1.5205</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4205</v>
+        <v>-1.4169</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7048</v>
+        <v>-1.7032</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2843</v>
+        <v>0.2863</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2673</v>
+        <v>-0.2713</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9384</v>
+        <v>-0.9415</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6711</v>
+        <v>0.6703</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1532</v>
+        <v>-1.1457</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7664</v>
+        <v>-0.7617</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3868</v>
+        <v>-0.384</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6038</v>
+        <v>-0.1429</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6751</v>
+        <v>-0.5601</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0713</v>
+        <v>0.4171</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9629</v>
+        <v>-3.1797</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2858</v>
+        <v>-1.5848</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6771</v>
+        <v>-1.5949</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.0909</v>
+        <v>-3.0835</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2788</v>
+        <v>-1.2755</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8121</v>
+        <v>-1.808</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3864</v>
+        <v>-0.3906</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1788</v>
+        <v>0.1756</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5652</v>
+        <v>-0.5662</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.7046</v>
+        <v>-2.6929</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4577</v>
+        <v>-1.4511</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2469</v>
+        <v>-1.2417</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2582</v>
+        <v>0.5168</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7635</v>
+        <v>-0.0561</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5053</v>
+        <v>0.5729</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.883399999999998</v>
+        <v>4.673499999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>12.4068</v>
+        <v>12.2339</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.523299999999999</v>
+        <v>-7.5605</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2664000000000009</v>
+        <v>-0.2621000000000002</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7424</v>
+        <v>2.729900000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.0092</v>
+        <v>-2.9922</v>
       </c>
       <c r="J24" t="n">
-        <v>14.9223</v>
+        <v>14.8238</v>
       </c>
       <c r="K24" t="n">
-        <v>7.326100000000001</v>
+        <v>7.2601</v>
       </c>
       <c r="L24" t="n">
-        <v>7.596000000000001</v>
+        <v>7.563399999999998</v>
       </c>
       <c r="M24" t="n">
-        <v>-15.189</v>
+        <v>-15.0859</v>
       </c>
       <c r="N24" t="n">
-        <v>-4.5838</v>
+        <v>-4.5303</v>
       </c>
       <c r="O24" t="n">
-        <v>-10.6051</v>
+        <v>-10.5555</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.543699999999999</v>
+        <v>-4.552499999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-11.3593</v>
+        <v>-11.3817</v>
       </c>
       <c r="R24" t="n">
-        <v>6.815799999999999</v>
+        <v>6.829000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>4.101700000000001</v>
+        <v>4.9011</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2287</v>
+        <v>-1.2577</v>
       </c>
       <c r="U24" t="n">
-        <v>5.3306</v>
+        <v>6.158699999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>4.5919</v>
+        <v>4.587199999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>10.0728</v>
+        <v>10.0493</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.481</v>
+        <v>-5.4623</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104722_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104722_W30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-10.0493</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104722_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-5.4623</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
